--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_404_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_404_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>8</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>9</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>66:06</t>
+          <t>26:06</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>29.0%</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>25:11</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -1647,22 +1647,22 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>30.4%</t>
         </is>
       </c>
     </row>
@@ -1733,10 +1733,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>4</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>62:09</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>11.7%</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>37:31</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AN20" t="n">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>8.1%</t>
         </is>
       </c>
     </row>
@@ -2125,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>5</v>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>38:23</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AN21" t="n">
@@ -2235,22 +2235,22 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>11.2%</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>28:16</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AN22" t="n">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>17.4%</t>
         </is>
       </c>
     </row>
@@ -2514,13 +2514,13 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>4</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>46:43</t>
+          <t>26:42</t>
         </is>
       </c>
       <c r="AN23" t="n">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AN24" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>03:31</t>
         </is>
       </c>
       <c r="AN25" t="n">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -3295,7 +3295,7 @@
         <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AN27" t="n">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
@@ -3494,13 +3494,13 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>1</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>44:09</t>
+          <t>24:04</t>
         </is>
       </c>
       <c r="AN28" t="n">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>28.9%</t>
         </is>
       </c>
     </row>
@@ -3827,16 +3827,16 @@
         <v>99</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>22</v>
@@ -4292,16 +4292,16 @@
         <v>14</v>
       </c>
       <c r="T35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>2</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>40:37</t>
+          <t>30:33</t>
         </is>
       </c>
       <c r="AN35" t="n">
@@ -4408,22 +4408,22 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>49.8%</t>
         </is>
       </c>
     </row>
@@ -4488,16 +4488,16 @@
         <v>5</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>2</v>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>72:21</t>
+          <t>32:23</t>
         </is>
       </c>
       <c r="AN36" t="n">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -4684,16 +4684,16 @@
         <v>24</v>
       </c>
       <c r="T37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>8</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>60:34</t>
+          <t>30:32</t>
         </is>
       </c>
       <c r="AN37" t="n">
@@ -4800,22 +4800,22 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>24.9%</t>
         </is>
       </c>
     </row>
@@ -5082,10 +5082,10 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AN39" t="n">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>59:50</t>
+          <t>29:48</t>
         </is>
       </c>
       <c r="AN40" t="n">
@@ -5388,22 +5388,22 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>10.4%</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="AN41" t="n">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>32:59</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AN42" t="n">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>63:23</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AN43" t="n">
@@ -5976,17 +5976,17 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>05:33</t>
         </is>
       </c>
       <c r="AN45" t="n">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AN46" t="n">
@@ -6564,17 +6564,17 @@
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
@@ -6784,16 +6784,16 @@
         <v>64</v>
       </c>
       <c r="T48" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
         <v>17</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_404_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_404_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M2" t="n">
         <v>8</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M3" t="n">
         <v>9</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1733,10 +1733,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X19" t="n">
         <v>4</v>
@@ -2125,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X21" t="n">
         <v>5</v>
@@ -2318,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2514,13 +2514,13 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
         <v>4</v>
@@ -3295,7 +3295,7 @@
         <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -3494,13 +3494,13 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
         <v>1</v>
@@ -3827,16 +3827,16 @@
         <v>99</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X30" t="n">
         <v>22</v>
@@ -4292,16 +4292,16 @@
         <v>14</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
         <v>2</v>
@@ -4488,16 +4488,16 @@
         <v>5</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
         <v>2</v>
@@ -4684,16 +4684,16 @@
         <v>24</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X37" t="n">
         <v>8</v>
@@ -5082,10 +5082,10 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -5275,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>64</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X48" t="n">
         <v>17</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_404_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_404_EL.xlsx
@@ -674,10 +674,10 @@
         <v>8</v>
       </c>
       <c r="N2" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>88.00</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="O3" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="P3" t="n">
         <v>5</v>
@@ -851,20 +851,20 @@
         <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1543,14 +1543,14 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y18" t="n">
         <v>4</v>
       </c>
-      <c r="Y18" t="n">
-        <v>5</v>
-      </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -2131,14 +2131,14 @@
         <v>2</v>
       </c>
       <c r="X21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA21" t="n">
@@ -2523,14 +2523,14 @@
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -3111,14 +3111,14 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3307,14 +3307,14 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3503,14 +3503,14 @@
         <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA28" t="n">
@@ -3839,14 +3839,14 @@
         <v>6</v>
       </c>
       <c r="X30" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="Y30" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4304,14 +4304,14 @@
         <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -4696,10 +4696,10 @@
         <v>4</v>
       </c>
       <c r="X37" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -5284,10 +5284,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
@@ -5317,25 +5317,25 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
@@ -6300,7 +6300,7 @@
         <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
@@ -6460,14 +6460,14 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA46" t="n">
@@ -6796,14 +6796,14 @@
         <v>7</v>
       </c>
       <c r="X48" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="Y48" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="AA48" t="n">
@@ -6829,25 +6829,25 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH48" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK48" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
